--- a/DATA/A098460_valuation.xlsx
+++ b/DATA/A098460_valuation.xlsx
@@ -396,40 +396,40 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>50728051.03929299</v>
+        <v>50392979.91983175</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>48919978.45773502</v>
+        <v>48750351.2351895</v>
       </c>
       <c r="B3">
         <v>4.815114820567475</v>
       </c>
       <c r="C3">
-        <v>235555313.2936815</v>
+        <v>234738538.7404309</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>51126266.6063676</v>
+        <v>50445236.74655022</v>
       </c>
       <c r="B4">
         <v>4.675741439609864</v>
       </c>
       <c r="C4">
-        <v>239053203.4239349</v>
+        <v>235868883.8867751</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>50485819.02133325</v>
+        <v>49970141.35112607</v>
       </c>
       <c r="B5">
         <v>5.422377961759365</v>
       </c>
       <c r="C5">
-        <v>273753192.4426491</v>
+        <v>270956993.2083464</v>
       </c>
     </row>
     <row r="6" spans="1:3">
